--- a/uploads/parallel_classes.xlsx
+++ b/uploads/parallel_classes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\float_working2\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349900DC-BEEA-4DF8-9DE0-B4A5E7C13B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E842010-150C-48BB-AA17-F4FE67AA09E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C330C10B-EC4B-49AB-845A-3F2FB1087177}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="43">
   <si>
     <t>MONDAY</t>
   </si>
@@ -156,6 +156,18 @@
   </si>
   <si>
     <t>12.45_-_1.30</t>
+  </si>
+  <si>
+    <t>S8_CSE</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>CSA</t>
+  </si>
+  <si>
+    <t>BCT</t>
   </si>
 </sst>
 </file>
@@ -533,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5D0D03-81CF-468A-A9D4-BE2ADA3ECDE1}">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="14.109375" customWidth="1"/>
@@ -2018,6 +2030,346 @@
         <v>28</v>
       </c>
     </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C88" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C89" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>39</v>
+      </c>
+      <c r="B90" t="s">
+        <v>0</v>
+      </c>
+      <c r="C90" t="s">
+        <v>36</v>
+      </c>
+      <c r="D90" t="s">
+        <v>23</v>
+      </c>
+      <c r="E90" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" t="s">
+        <v>0</v>
+      </c>
+      <c r="C91" t="s">
+        <v>36</v>
+      </c>
+      <c r="D91" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>39</v>
+      </c>
+      <c r="B92" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" t="s">
+        <v>34</v>
+      </c>
+      <c r="D92" t="s">
+        <v>23</v>
+      </c>
+      <c r="E92" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>39</v>
+      </c>
+      <c r="B93" t="s">
+        <v>3</v>
+      </c>
+      <c r="C93" t="s">
+        <v>34</v>
+      </c>
+      <c r="D93" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>39</v>
+      </c>
+      <c r="B94" t="s">
+        <v>3</v>
+      </c>
+      <c r="C94" t="s">
+        <v>35</v>
+      </c>
+      <c r="D94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E94" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>39</v>
+      </c>
+      <c r="B95" t="s">
+        <v>3</v>
+      </c>
+      <c r="C95" t="s">
+        <v>35</v>
+      </c>
+      <c r="D95" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>39</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>37</v>
+      </c>
+      <c r="D96" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>39</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>37</v>
+      </c>
+      <c r="D97" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>39</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>38</v>
+      </c>
+      <c r="D98" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>39</v>
+      </c>
+      <c r="B99" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" t="s">
+        <v>38</v>
+      </c>
+      <c r="D99" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>39</v>
+      </c>
+      <c r="B100" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" t="s">
+        <v>37</v>
+      </c>
+      <c r="D100" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>39</v>
+      </c>
+      <c r="B101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" t="s">
+        <v>37</v>
+      </c>
+      <c r="D101" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>39</v>
+      </c>
+      <c r="B102" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" t="s">
+        <v>38</v>
+      </c>
+      <c r="D102" t="s">
+        <v>23</v>
+      </c>
+      <c r="E102" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>39</v>
+      </c>
+      <c r="B103" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" t="s">
+        <v>38</v>
+      </c>
+      <c r="D103" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>39</v>
+      </c>
+      <c r="B104" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" t="s">
+        <v>34</v>
+      </c>
+      <c r="D104" t="s">
+        <v>23</v>
+      </c>
+      <c r="E104" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>39</v>
+      </c>
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" t="s">
+        <v>34</v>
+      </c>
+      <c r="D105" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>39</v>
+      </c>
+      <c r="B106" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" t="s">
+        <v>33</v>
+      </c>
+      <c r="D106" t="s">
+        <v>23</v>
+      </c>
+      <c r="E106" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>39</v>
+      </c>
+      <c r="B107" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" t="s">
+        <v>33</v>
+      </c>
+      <c r="D107" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
